--- a/stories/arbres/ATOM-SEC.PAR.001-13.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-13.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Didier arrive au parc avec papa. Papa montre le bac à sable. C'est l'espace montré. Didier s'assoit dans le sable. Le sable est frais. Il remplit un seau. Papa s'assoit sur le banc. L'adulte voit Didier. Didier reste dans l'espace montré. Papa dit : je te vois. L'adulte voit. Plus tard, papa montre les plots jaunes. Autre lieu, même leçon. C'est encore l'espace montré. Didier saute de plot en plot. Ses pieds tapent le caoutchouc. Il reste là où papa a dit. Papa le voit. Didier range le seau. Il reste près. L'espace montré, c'est ici. L'adulte voit.</t>
+          <t>Didier arrive au parc avec papa. Papa montre le bac à sable. C'est l'espace montré. Didier s'assoit dans le sable. Le sable est frais. Il remplit un seau. Papa s'assoit sur le banc. L'adulte voit Didier. Didier reste dans l'espace montré. Je te vois. L'adulte voit. Plus tard, papa montre les plots jaunes. Autre lieu, même leçon. C'est encore l'espace montré. Didier saute de plot en plot. Ses pieds tapent le caoutchouc. Il reste là où papa a dit. Papa le voit. Didier range le seau. Il reste près. L'espace montré, c'est ici. L'adulte voit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Didier arrive au parc avec papa. Papa montre le bac à sable. C'est l'espace montré. Didier s'assoit dans le sable. Le sable est frais. Il remplit un seau. Papa s'assoit sur le banc. L'adulte voit Didier. Didier reste dans l'espace montré.
+papa|Je te vois. L'adulte voit. Plus tard, papa montre les plots jaunes. Autre lieu, même leçon. C'est encore l'espace montré.
+narrateur|Didier saute de plot en plot. Ses pieds tapent le caoutchouc. Il reste là où papa a dit. Papa le voit. Didier range le seau. Il reste près. L'espace montré, c'est ici. L'adulte voit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1488,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Didier joue au parc. Où reste-t-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1661,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Didier est resté dans l'espace montré. Au bac, puis aux plots. L'adulte voit.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1828,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Didier prend la main de papa. Ils quittent le parc.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1995,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2035,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.PAR.001-13.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-13.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,11 @@
 narrateur|Didier saute de plot en plot. Ses pieds tapent le caoutchouc. Il reste là où papa a dit. Papa le voit. Didier range le seau. Il reste près. L'espace montré, c'est ici. L'adulte voit.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1493,6 +1503,11 @@
       <c r="AW3" t="inlineStr">
         <is>
           <t>narrateur|Didier joue au parc. Où reste-t-il ?</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
         </is>
       </c>
     </row>
@@ -1666,6 +1681,7 @@
           <t>narrateur|Didier est resté dans l'espace montré. Au bac, puis aux plots. L'adulte voit.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1849,11 @@
           <t>narrateur|Didier prend la main de papa. Ils quittent le parc.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2000,6 +2021,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2018,7 +2040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2064,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2243,6 +2279,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.PAR.001-13.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-13.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Didier joue où papa peut voir</t>
+          <t>Les plots jaunes de Victorino</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Victorino fait un château puis saute de plot en plot, dans l'espace que papa a montré.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Didier arrive au parc avec papa. Papa montre le bac à sable. C'est l'espace montré. Didier s'assoit dans le sable. Le sable est frais. Il remplit un seau. Papa s'assoit sur le banc. L'adulte voit Didier. Didier reste dans l'espace montré. Je te vois. L'adulte voit. Plus tard, papa montre les plots jaunes. Autre lieu, même leçon. C'est encore l'espace montré. Didier saute de plot en plot. Ses pieds tapent le caoutchouc. Il reste là où papa a dit. Papa le voit. Didier range le seau. Il reste près. L'espace montré, c'est ici. L'adulte voit.</t>
+          <t>Un plot jaune sent le caoutchouc chaud. Le parc sent l'herbe et le soleil. Le sol souple rebondit un peu. Une coccinelle grimpe sur un plot. Le seau bleu attend près du bac. Papa pose le sac contre le banc. Tu as vu la coccinelle, Victorino ? Oui, papa. Elle est rouge. En ce moment, papa montre le bac à sable. C'est l'espace montré. Tu joues ici. L'adulte voit. Ici, papa ? Oui. On reste dans l'espace montré. Victorino s'assoit dans le sable. Le sable est frais. Il remplit un seau. Papa s'assoit sur le banc. L'adulte voit Victorino. Victorino reste dans l'espace montré. Je te vois. L'adulte voit. Tu me vois ? Oui. Le seau bleu devient lourd. Victorino le verse, tout doucement. Un château. Un petit château. Tu joues là où l'adulte a dit. Plus tard, papa montre les plots jaunes. C'est encore l'espace montré. Ici, l'adulte voit. Je peux sauter ? Oui. Tu restes dans l'espace montré. Victorino saute de plot en plot. Ses pieds tapent le caoutchouc. Le sol fait poum, tout mou. Il reste là où papa a dit. Papa le voit. L'adulte voit. Tu restes là où l'adulte a dit ? Oui. Sur les plots. Bravo, Victorino. Tu as fait du bon travail. Victorino range le seau. Il reste près. L'espace montré, c'est ici. L'adulte voit. Tu as fini de sauter ? Oui, papa. Bravo. La coccinelle a quitté le plot. Le caoutchouc reste chaud. Victorino pose la main dessus. C'est mou. Oui. Le sol est souple. Il reste dans l'espace montré. L'adulte voit. Le château de sable tient encore. Victorino lisse un mur, tout fin. Il est petit. Oui. Tu as joué dans l'espace montré. Dans l'espace montré. Bravo. Un plot jaune penche un peu. Victorino le redresse. Ses pieds restent sur le caoutchouc.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,9 +1324,79 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Didier arrive au parc avec papa. Papa montre le bac à sable. C'est l'espace montré. Didier s'assoit dans le sable. Le sable est frais. Il remplit un seau. Papa s'assoit sur le banc. L'adulte voit Didier. Didier reste dans l'espace montré.
-papa|Je te vois. L'adulte voit. Plus tard, papa montre les plots jaunes. Autre lieu, même leçon. C'est encore l'espace montré.
-narrateur|Didier saute de plot en plot. Ses pieds tapent le caoutchouc. Il reste là où papa a dit. Papa le voit. Didier range le seau. Il reste près. L'espace montré, c'est ici. L'adulte voit.</t>
+          <t>narrateur|Un plot jaune sent le caoutchouc chaud.
+narrateur|Le parc sent l'herbe et le soleil.
+narrateur|Le sol souple rebondit un peu.
+narrateur|Une coccinelle grimpe sur un plot.
+narrateur|Le seau bleu attend près du bac.
+narrateur|Papa pose le sac contre le banc.
+papa|Tu as vu la coccinelle, Victorino ?
+enfant-m|Oui, papa.
+enfant-m|Elle est rouge.
+narrateur|En ce moment, papa montre le bac à sable.
+papa|C'est l'espace montré.
+papa|Tu joues ici.
+papa|L'adulte voit.
+enfant-m|Ici, papa ?
+papa|Oui.
+papa|On reste dans l'espace montré.
+narrateur|Victorino s'assoit dans le sable.
+narrateur|Le sable est frais.
+narrateur|Il remplit un seau.
+narrateur|Papa s'assoit sur le banc.
+narrateur|L'adulte voit Victorino.
+narrateur|Victorino reste dans l'espace montré.
+papa|Je te vois.
+papa|L'adulte voit.
+enfant-m|Tu me vois ?
+papa|Oui.
+narrateur|Le seau bleu devient lourd.
+narrateur|Victorino le verse, tout doucement.
+enfant-m|Un château.
+papa|Un petit château.
+papa|Tu joues là où l'adulte a dit.
+narrateur|Plus tard, papa montre les plots jaunes.
+papa|C'est encore l'espace montré.
+papa|Ici, l'adulte voit.
+enfant-m|Je peux sauter ?
+papa|Oui.
+papa|Tu restes dans l'espace montré.
+narrateur|Victorino saute de plot en plot.
+narrateur|Ses pieds tapent le caoutchouc.
+narrateur|Le sol fait poum, tout mou.
+narrateur|Il reste là où papa a dit.
+narrateur|Papa le voit.
+narrateur|L'adulte voit.
+papa|Tu restes là où l'adulte a dit ?
+enfant-m|Oui.
+enfant-m|Sur les plots.
+papa|Bravo, Victorino.
+papa|Tu as fait du bon travail.
+narrateur|Victorino range le seau.
+narrateur|Il reste près.
+narrateur|L'espace montré, c'est ici.
+narrateur|L'adulte voit.
+papa|Tu as fini de sauter ?
+enfant-m|Oui, papa.
+papa|Bravo.
+narrateur|La coccinelle a quitté le plot.
+narrateur|Le caoutchouc reste chaud.
+narrateur|Victorino pose la main dessus.
+enfant-m|C'est mou.
+papa|Oui.
+papa|Le sol est souple.
+narrateur|Il reste dans l'espace montré.
+narrateur|L'adulte voit.
+narrateur|Le château de sable tient encore.
+narrateur|Victorino lisse un mur, tout fin.
+enfant-m|Il est petit.
+papa|Oui.
+papa|Tu as joué dans l'espace montré.
+enfant-m|Dans l'espace montré.
+papa|Bravo.
+narrateur|Un plot jaune penche un peu.
+narrateur|Victorino le redresse.
+narrateur|Ses pieds restent sur le caoutchouc.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1346,7 +1428,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Didier joue au parc. Où reste-t-il ?</t>
+          <t>Victorino joue au parc. Où reste-t-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,7 +1584,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Didier joue au parc. Où reste-t-il ?</t>
+          <t>narrateur|Victorino joue au parc.
+narrateur|Où reste-t-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1534,7 +1617,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Didier est resté dans l'espace montré. Au bac, puis aux plots. L'adulte voit.</t>
+          <t>Victorino est resté dans l'espace montré. Au bac, puis aux plots. L'adulte voit. Tu es resté dans l'espace montré ? Oui. Au bac, puis aux plots. Bravo. L'adulte voit. Le plot jaune brille encore.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1678,7 +1761,15 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Didier est resté dans l'espace montré. Au bac, puis aux plots. L'adulte voit.</t>
+          <t>narrateur|Victorino est resté dans l'espace montré.
+narrateur|Au bac, puis aux plots.
+narrateur|L'adulte voit.
+papa|Tu es resté dans l'espace montré ?
+enfant-m|Oui.
+enfant-m|Au bac, puis aux plots.
+papa|Bravo.
+papa|L'adulte voit.
+narrateur|Le plot jaune brille encore.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1706,7 +1797,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Didier prend la main de papa. Ils quittent le parc.</t>
+          <t>Victorino prend la main de papa. Tu as fini de ranger le seau ? Oui, papa. Bravo. Ils quittent le parc. Le caoutchouc redevient calme. Le seau bleu reste près du bac.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1846,7 +1937,13 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Didier prend la main de papa. Ils quittent le parc.</t>
+          <t>narrateur|Victorino prend la main de papa.
+papa|Tu as fini de ranger le seau ?
+enfant-m|Oui, papa.
+papa|Bravo.
+narrateur|Ils quittent le parc.
+narrateur|Le caoutchouc redevient calme.
+narrateur|Le seau bleu reste près du bac.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1878,7 +1975,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Un plot jaune garde le soleil. On a sauté. Oui. Dans l'espace montré. Bravo, Victorino. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2018,7 +2115,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Un plot jaune garde le soleil.
+enfant-m|On a sauté.
+papa|Oui.
+papa|Dans l'espace montré.
+papa|Bravo, Victorino.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2040,7 +2142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2078,6 +2180,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.PAR.001-13.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-13.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un plot jaune sent le caoutchouc chaud. Le parc sent l'herbe et le soleil. Le sol souple rebondit un peu. Une coccinelle grimpe sur un plot. Le seau bleu attend près du bac. Papa pose le sac contre le banc. Tu as vu la coccinelle, Victorino ? Oui, papa. Elle est rouge. En ce moment, papa montre le bac à sable. C'est l'espace montré. Tu joues ici. L'adulte voit. Ici, papa ? Oui. On reste dans l'espace montré. Victorino s'assoit dans le sable. Le sable est frais. Il remplit un seau. Papa s'assoit sur le banc. L'adulte voit Victorino. Victorino reste dans l'espace montré. Je te vois. L'adulte voit. Tu me vois ? Oui. Le seau bleu devient lourd. Victorino le verse, tout doucement. Un château. Un petit château. Tu joues là où l'adulte a dit. Plus tard, papa montre les plots jaunes. C'est encore l'espace montré. Ici, l'adulte voit. Je peux sauter ? Oui. Tu restes dans l'espace montré. Victorino saute de plot en plot. Ses pieds tapent le caoutchouc. Le sol fait poum, tout mou. Il reste là où papa a dit. Papa le voit. L'adulte voit. Tu restes là où l'adulte a dit ? Oui. Sur les plots. Bravo, Victorino. Tu as fait du bon travail. Victorino range le seau. Il reste près. L'espace montré, c'est ici. L'adulte voit. Tu as fini de sauter ? Oui, papa. Bravo. La coccinelle a quitté le plot. Le caoutchouc reste chaud. Victorino pose la main dessus. C'est mou. Oui. Le sol est souple. Il reste dans l'espace montré. L'adulte voit. Le château de sable tient encore. Victorino lisse un mur, tout fin. Il est petit. Oui. Tu as joué dans l'espace montré. Dans l'espace montré. Bravo. Un plot jaune penche un peu. Victorino le redresse. Ses pieds restent sur le caoutchouc.</t>
+          <t>Un plot jaune sent le caoutchouc chaud. Le parc sent l'herbe et le soleil. Le sol souple rebondit un peu. Une coccinelle grimpe sur un plot. Le seau bleu attend près du bac. Papa pose le sac contre le banc. Tu as vu la coccinelle, Victorino ? Oui, papa. Elle est rouge. En ce moment, papa montre le bac à sable. C'est l'espace montré. Tu joues ici. L'adulte voit. Ici, papa ? Oui. On reste dans l'espace montré. Victorino s'assoit dans le sable. Le sable est frais. Il remplit un seau. Papa s'assoit sur le banc. L'adulte voit Victorino. Victorino reste dans l'espace montré. Je te vois. L'adulte voit. Tu me vois ? Oui. Le seau bleu devient lourd. Victorino le verse, tout doucement. Un château. Un petit château. Tu joues là où l'adulte a dit. Plus tard, papa montre les plots jaunes. C'est encore l'espace montré. Ici, l'adulte voit. Je peux sauter ? Oui. Tu restes dans l'espace montré. Victorino saute de plot en plot. Ses pieds tapent le caoutchouc. Le sol fait poum, tout mou. Il reste là où papa a dit. Papa le voit. L'adulte voit. Tu restes là où l'adulte a dit ? Oui. Sur les plots. Bravo, Victorino. Victorino range le seau. Il reste près. L'espace montré, c'est ici. L'adulte voit. Tu as fini de sauter ? Oui, papa. Bravo. La coccinelle a quitté le plot. Le caoutchouc reste chaud. Victorino pose la main dessus. C'est mou. Oui. Le sol est souple. Il reste dans l'espace montré. L'adulte voit. Le château de sable tient encore. Victorino lisse un mur, tout fin. Il est petit. Oui. Tu as joué dans l'espace montré. Dans l'espace montré. Bravo. Un plot jaune penche un peu. Victorino le redresse. Ses pieds restent sur le caoutchouc.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Didier arrive au parc avec papa. Papa montre le bac à sable. C'est l'&lt;emphasis level="moderate"&gt;espace&lt;/emphasis&gt; montré. Didier s'assoit dans le sable. Le sable est frais. Il remplit un seau. Papa s'assoit sur le banc. L'adulte voit Didier. Didier reste dans l'espace montré. Papa dit : je te vois. L'adulte voit. Plus tard, papa montre les plots jaunes. Autre lieu, même leçon. C'est encore l'espace montré. Didier saute de plot en plot. Ses pieds tapent le caoutchouc. Il reste là où papa a dit. Papa le voit. Didier range le seau. Il reste près. L'espace montré, c'est ici. L'adulte voit.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un plot jaune sent le caoutchouc chaud. Le parc sent l'herbe et le soleil. Le sol souple rebondit un peu. Une coccinelle grimpe sur un plot. Le seau bleu attend près du bac. Papa pose le sac contre le banc. Tu as vu la coccinelle, Victorino ? Oui, papa. Elle est rouge. En ce moment, papa montre le bac à sable. C'est l'espace montré. Tu joues ici. L'adulte voit. Ici, papa ? Oui. On reste dans l'espace montré. Victorino s'assoit dans le sable. Le sable est frais. Il remplit un seau. Papa s'assoit sur le banc. L'adulte voit Victorino. Victorino reste dans l'espace montré. Je te vois. L'adulte voit. Tu me vois ? Oui. Le seau bleu devient lourd. Victorino le verse, tout doucement. Un château. Un petit château. Tu joues là où l'adulte a dit. Plus tard, papa montre les plots jaunes. C'est encore l'espace montré. Ici, l'adulte voit. Je peux sauter ? Oui. Tu restes dans l'espace montré. Victorino saute de plot en plot. Ses pieds tapent le caoutchouc. Le sol fait poum, tout mou. Il reste là où papa a dit. Papa le voit. L'adulte voit. Tu restes là où l'adulte a dit ? Oui. Sur les plots. Bravo, Victorino. Victorino range le seau. Il reste près. L'espace montré, c'est ici. L'adulte voit. Tu as fini de sauter ? Oui, papa. Bravo. La coccinelle a quitté le plot. Le caoutchouc reste chaud. Victorino pose la main dessus. C'est mou. Oui. Le sol est souple. Il reste dans l'espace montré. L'adulte voit. Le château de sable tient encore. Victorino lisse un mur, tout fin. Il est petit. Oui. Tu as joué dans l'espace montré. Dans l'espace montré. Bravo. Un plot jaune penche un peu. Victorino le redresse. Ses pieds restent sur le caoutchouc.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1371,7 +1371,6 @@
 enfant-m|Oui.
 enfant-m|Sur les plots.
 papa|Bravo, Victorino.
-papa|Tu as fait du bon travail.
 narrateur|Victorino range le seau.
 narrateur|Il reste près.
 narrateur|L'espace montré, c'est ici.
@@ -1433,7 +1432,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Didier joue au parc. Où reste-t-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino joue au parc. Où reste-t-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1622,7 +1621,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Didier est resté dans l'&lt;emphasis level="moderate"&gt;espace&lt;/emphasis&gt; montré. Au bac, puis aux plots. L'adulte voit.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino est resté dans l'espace montré. Au bac, puis aux plots. L'adulte voit. Tu es resté dans l'espace montré ? Oui. Au bac, puis aux plots. Bravo. L'adulte voit. Le plot jaune brille encore.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1772,7 +1771,6 @@
 narrateur|Le plot jaune brille encore.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1802,7 +1800,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Didier prend la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; de papa. Ils quittent le parc.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino prend la main de papa. Tu as fini de ranger le seau ? Oui, papa. Bravo. Ils quittent le parc. Le caoutchouc redevient calme. Le seau bleu reste près du bac.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1975,12 +1973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Un plot jaune garde le soleil. On a sauté. Oui. Dans l'espace montré. Bravo, Victorino. L'histoire est finie.</t>
+          <t>Un plot jaune garde le soleil. On a sauté. Oui. Dans l'espace montré. Bravo, Victorino.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un plot jaune garde le soleil. On a sauté. Oui. Dans l'espace montré. Bravo, Victorino.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2119,11 +2117,9 @@
 enfant-m|On a sauté.
 papa|Oui.
 papa|Dans l'espace montré.
-papa|Bravo, Victorino.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+papa|Bravo, Victorino.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2142,7 +2138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2187,6 +2183,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.PAR.001-13.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-13.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Didier, papa</t>
+          <t>Victorino, papa</t>
         </is>
       </c>
     </row>
